--- a/research/traditional_assets/database/data/hong_kong/hong_kong_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_cable_tv.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06065</v>
+        <v>-0.0573</v>
       </c>
       <c r="G2">
-        <v>-0.1554844318002213</v>
+        <v>-0.468</v>
       </c>
       <c r="H2">
-        <v>-0.1595542911332385</v>
+        <v>-0.4724890829694323</v>
       </c>
       <c r="I2">
-        <v>-0.3377004675082503</v>
+        <v>-0.6700341884845192</v>
       </c>
       <c r="J2">
-        <v>-0.3377004675082503</v>
+        <v>-0.6700341884845192</v>
       </c>
       <c r="K2">
-        <v>-59.53</v>
+        <v>-109.3</v>
       </c>
       <c r="L2">
-        <v>-0.4704441283388652</v>
+        <v>-0.9545851528384279</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8.059000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="V2">
-        <v>0.1334271523178808</v>
+        <v>0.2810289389067524</v>
       </c>
       <c r="W2">
-        <v>-1.297865051200023</v>
+        <v>10.7156862745098</v>
       </c>
       <c r="X2">
-        <v>0.153652238482627</v>
+        <v>0.228854405145249</v>
       </c>
       <c r="Y2">
-        <v>-1.45151728968265</v>
+        <v>10.48683186936456</v>
       </c>
       <c r="Z2">
-        <v>0.9090772867612156</v>
+        <v>0.9903595811552232</v>
       </c>
       <c r="AA2">
-        <v>-0.5038990527247178</v>
+        <v>-0.6635747782672083</v>
       </c>
       <c r="AB2">
-        <v>0.08428426276233279</v>
+        <v>0.07443558732986022</v>
       </c>
       <c r="AC2">
-        <v>-0.5881833154870506</v>
+        <v>-0.7380103655970686</v>
       </c>
       <c r="AD2">
-        <v>137.46</v>
+        <v>181</v>
       </c>
       <c r="AE2">
-        <v>0.2180857924699574</v>
+        <v>0.09457290738722164</v>
       </c>
       <c r="AF2">
-        <v>137.6780857924699</v>
+        <v>181.0945729073872</v>
       </c>
       <c r="AG2">
-        <v>129.6190857924699</v>
+        <v>172.3545729073872</v>
       </c>
       <c r="AH2">
-        <v>0.6950697511117803</v>
+        <v>0.8534364023835159</v>
       </c>
       <c r="AI2">
-        <v>1.021365288557835</v>
+        <v>2.940105992449669</v>
       </c>
       <c r="AJ2">
-        <v>0.6821371929661524</v>
+        <v>0.8471403244686136</v>
       </c>
       <c r="AK2">
-        <v>1.022723850199739</v>
+        <v>3.260920738294304</v>
       </c>
       <c r="AL2">
-        <v>7.292</v>
+        <v>8.43</v>
       </c>
       <c r="AM2">
-        <v>7.105</v>
+        <v>8.33</v>
       </c>
       <c r="AN2">
-        <v>-6.567920110850971</v>
+        <v>-2.82371294851794</v>
       </c>
       <c r="AO2">
-        <v>-5.883159626988481</v>
+        <v>-9.110320284697508</v>
       </c>
       <c r="AP2">
-        <v>-6.193276591928422</v>
+        <v>-2.688838890910877</v>
       </c>
       <c r="AQ2">
-        <v>-6.038001407459536</v>
+        <v>-9.219687875150059</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0707</v>
+        <v>-0.0573</v>
       </c>
       <c r="G3">
-        <v>-0.1421253175275191</v>
+        <v>-0.468</v>
       </c>
       <c r="H3">
-        <v>-0.1464860287891618</v>
+        <v>-0.4724890829694323</v>
       </c>
       <c r="I3">
-        <v>-0.3254243620532938</v>
+        <v>-0.6700341884845192</v>
       </c>
       <c r="J3">
-        <v>-0.3254243620532938</v>
+        <v>-0.6700341884845192</v>
       </c>
       <c r="K3">
-        <v>-52.8</v>
+        <v>-109.3</v>
       </c>
       <c r="L3">
-        <v>-0.4470787468247248</v>
+        <v>-0.9545851528384279</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,201 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.98</v>
+        <v>8.74</v>
       </c>
       <c r="V3">
-        <v>0.2353982300884956</v>
+        <v>0.2810289389067524</v>
       </c>
       <c r="W3">
-        <v>-1.225058004640371</v>
+        <v>10.7156862745098</v>
       </c>
       <c r="X3">
-        <v>0.2210766466931244</v>
+        <v>0.228854405145249</v>
       </c>
       <c r="Y3">
-        <v>-1.446134651333496</v>
+        <v>10.48683186936456</v>
       </c>
       <c r="Z3">
-        <v>0.8865162661470661</v>
+        <v>0.9903595811552232</v>
       </c>
       <c r="AA3">
-        <v>-0.2884939903607771</v>
+        <v>-0.6635747782672083</v>
       </c>
       <c r="AB3">
-        <v>0.08619336505271713</v>
+        <v>0.07443558732986022</v>
       </c>
       <c r="AC3">
-        <v>-0.3746873554134942</v>
+        <v>-0.7380103655970686</v>
       </c>
       <c r="AD3">
-        <v>133.7</v>
+        <v>181</v>
       </c>
       <c r="AE3">
-        <v>0.2180857924699574</v>
+        <v>0.09457290738722164</v>
       </c>
       <c r="AF3">
-        <v>133.91808579247</v>
+        <v>181.0945729073872</v>
       </c>
       <c r="AG3">
-        <v>125.9380857924699</v>
+        <v>172.3545729073872</v>
       </c>
       <c r="AH3">
-        <v>0.7979955507184011</v>
+        <v>0.8534364023835159</v>
       </c>
       <c r="AI3">
-        <v>1.082445504508613</v>
+        <v>2.940105992449669</v>
       </c>
       <c r="AJ3">
-        <v>0.7879103729757189</v>
+        <v>0.8471403244686136</v>
       </c>
       <c r="AK3">
-        <v>1.088130021592802</v>
+        <v>3.260920738294304</v>
       </c>
       <c r="AL3">
-        <v>6.3</v>
+        <v>8.43</v>
       </c>
       <c r="AM3">
-        <v>6.114</v>
+        <v>8.33</v>
       </c>
       <c r="AN3">
-        <v>-7.96354756090297</v>
+        <v>-2.82371294851794</v>
       </c>
       <c r="AO3">
-        <v>-6.126984126984127</v>
+        <v>-9.110320284697508</v>
       </c>
       <c r="AP3">
-        <v>-7.501226147624632</v>
+        <v>-2.688838890910877</v>
       </c>
       <c r="AQ3">
-        <v>-6.313379129865882</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Farnova Group Holdings Limited (SEHK:8153)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cable TV</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.192</v>
-      </c>
-      <c r="G4">
-        <v>-0.3424170616113744</v>
-      </c>
-      <c r="H4">
-        <v>-0.3424170616113744</v>
-      </c>
-      <c r="I4">
-        <v>-0.509478672985782</v>
-      </c>
-      <c r="J4">
-        <v>-0.509478672985782</v>
-      </c>
-      <c r="K4">
-        <v>-6.73</v>
-      </c>
-      <c r="L4">
-        <v>-0.79739336492891</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.079</v>
-      </c>
-      <c r="V4">
-        <v>0.002981132075471698</v>
-      </c>
-      <c r="W4">
-        <v>-1.370672097759674</v>
-      </c>
-      <c r="X4">
-        <v>0.08622783027212964</v>
-      </c>
-      <c r="Y4">
-        <v>-1.456899928031804</v>
-      </c>
-      <c r="Z4">
-        <v>1.411843425894948</v>
-      </c>
-      <c r="AA4">
-        <v>-0.7193041150886584</v>
-      </c>
-      <c r="AB4">
-        <v>0.08237516047194846</v>
-      </c>
-      <c r="AC4">
-        <v>-0.8016792755606069</v>
-      </c>
-      <c r="AD4">
-        <v>3.76</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>3.76</v>
-      </c>
-      <c r="AG4">
-        <v>3.681</v>
-      </c>
-      <c r="AH4">
-        <v>0.124256444150694</v>
-      </c>
-      <c r="AI4">
-        <v>0.3393501805054152</v>
-      </c>
-      <c r="AJ4">
-        <v>0.1219641496305623</v>
-      </c>
-      <c r="AK4">
-        <v>0.3346059449140987</v>
-      </c>
-      <c r="AL4">
-        <v>0.992</v>
-      </c>
-      <c r="AM4">
-        <v>0.991</v>
-      </c>
-      <c r="AN4">
-        <v>-0.9082125603864735</v>
-      </c>
-      <c r="AO4">
-        <v>-4.334677419354839</v>
-      </c>
-      <c r="AP4">
-        <v>-0.8891304347826087</v>
-      </c>
-      <c r="AQ4">
-        <v>-4.339051463168516</v>
+        <v>-9.219687875150059</v>
       </c>
     </row>
   </sheetData>
